--- a/src/OpenXmlHtml.Tests/Samples/SpreadsheetSamples.BugReportSpreadsheet.Net.verified.xlsx
+++ b/src/OpenXmlHtml.Tests/Samples/SpreadsheetSamples.BugReportSpreadsheet.Net.verified.xlsx
@@ -184,9 +184,6 @@
 </t>
           </r>
           <r>
-            <t xml:space="preserve"> </t>
-          </r>
-          <r>
             <rPr>
               <b/>
             </rPr>
